--- a/output/StructureDefinition-ConsentModule.xlsx
+++ b/output/StructureDefinition-ConsentModule.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4383" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4383" uniqueCount="666">
   <si>
     <t>Property</t>
   </si>
@@ -1687,7 +1687,7 @@
 </t>
   </si>
   <si>
-    <t>Text als Markdown</t>
+    <t>String equivalent with markdown</t>
   </si>
   <si>
     <t>This is an equivalent of the string on which the extension is sent, but includes additional markdown (see documentation about [markdown](http://hl7.org/fhir/R4/datatypes.html#markdown). Note that using HTML  [xhtml](http://hl7.org/fhir/R4/extension-rendering-xhtml.html) can allow for greater precision of display.</t>
@@ -1718,10 +1718,6 @@
   </si>
   <si>
     <t>Questionnaire.item.text.extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
   </si>
   <si>
     <t>Questionnaire.item.text.extension:renderingMarkdown.value[x]:valueMarkdown</t>
@@ -12313,7 +12309,7 @@
         <v>530</v>
       </c>
       <c r="D97" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -12340,9 +12336,7 @@
       <c r="M97" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="N97" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>21</v>
@@ -12783,14 +12777,16 @@
         <v>21</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="AC101" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD101" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="AF101" t="s" s="2">
         <v>457</v>
@@ -12810,13 +12806,13 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>542</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D102" t="s" s="2">
         <v>21</v>
@@ -12912,16 +12908,16 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>528</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D103" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -12940,17 +12936,15 @@
         <v>21</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="L103" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="L103" t="s" s="2">
+      <c r="M103" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="M103" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>21</v>
@@ -13016,7 +13010,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>535</v>
@@ -13116,7 +13110,7 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>537</v>
@@ -13218,7 +13212,7 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>539</v>
@@ -13261,7 +13255,7 @@
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="S106" t="s" s="2">
         <v>21</v>
@@ -13320,7 +13314,7 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>542</v>
@@ -13391,14 +13385,16 @@
         <v>21</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="AC107" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD107" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="AF107" t="s" s="2">
         <v>457</v>
@@ -13418,13 +13414,13 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>542</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>21</v>
@@ -13520,10 +13516,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13549,10 +13545,10 @@
         <v>97</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -13576,34 +13572,34 @@
         <v>21</v>
       </c>
       <c r="W109" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF109" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="X109" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y109" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z109" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA109" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB109" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD109" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE109" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF109" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>75</v>
@@ -13620,10 +13616,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13649,16 +13645,16 @@
         <v>163</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="N110" t="s" s="2">
+      <c r="O110" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>21</v>
@@ -13686,11 +13682,11 @@
         <v>211</v>
       </c>
       <c r="Y110" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="Z110" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="Z110" t="s" s="2">
-        <v>568</v>
-      </c>
       <c r="AA110" t="s" s="2">
         <v>21</v>
       </c>
@@ -13707,7 +13703,7 @@
         <v>21</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>82</v>
@@ -13724,10 +13720,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13753,16 +13749,16 @@
         <v>422</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="M111" t="s" s="2">
+      <c r="N111" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="N111" t="s" s="2">
+      <c r="O111" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>21</v>
@@ -13811,7 +13807,7 @@
         <v>21</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>75</v>
@@ -13823,15 +13819,15 @@
         <v>94</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13928,10 +13924,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14030,10 +14026,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14134,10 +14130,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14163,13 +14159,13 @@
         <v>97</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -14219,7 +14215,7 @@
         <v>21</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>82</v>
@@ -14236,10 +14232,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14265,10 +14261,10 @@
         <v>163</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>340</v>
@@ -14300,11 +14296,11 @@
         <v>211</v>
       </c>
       <c r="Y116" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="Z116" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="Z116" t="s" s="2">
-        <v>586</v>
-      </c>
       <c r="AA116" t="s" s="2">
         <v>21</v>
       </c>
@@ -14321,7 +14317,7 @@
         <v>21</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>82</v>
@@ -14338,10 +14334,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14364,13 +14360,13 @@
         <v>21</v>
       </c>
       <c r="K117" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="L117" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="L117" t="s" s="2">
+      <c r="M117" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -14400,37 +14396,37 @@
         <v>153</v>
       </c>
       <c r="Y117" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="Z117" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="Z117" t="s" s="2">
+      <c r="AA117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI117" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="AG117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI117" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>95</v>
@@ -14438,10 +14434,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14467,13 +14463,13 @@
         <v>163</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="M118" t="s" s="2">
+      <c r="N118" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -14502,37 +14498,37 @@
         <v>211</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="Z118" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI118" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>95</v>
@@ -14540,10 +14536,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14569,74 +14565,74 @@
         <v>278</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q119" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="R119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI119" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="R119" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S119" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T119" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U119" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V119" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W119" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X119" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z119" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA119" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB119" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC119" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD119" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE119" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF119" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>95</v>
@@ -14644,10 +14640,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14673,23 +14669,23 @@
         <v>278</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="M120" t="s" s="2">
+      <c r="N120" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="N120" t="s" s="2">
+      <c r="O120" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="O120" t="s" s="2">
+      <c r="P120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q120" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="P120" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q120" t="s" s="2">
-        <v>611</v>
-      </c>
       <c r="R120" t="s" s="2">
         <v>21</v>
       </c>
@@ -14733,7 +14729,7 @@
         <v>21</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>75</v>
@@ -14742,7 +14738,7 @@
         <v>82</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>95</v>
@@ -14750,10 +14746,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14779,16 +14775,16 @@
         <v>278</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="M121" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="M121" t="s" s="2">
+      <c r="N121" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="N121" t="s" s="2">
+      <c r="O121" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>21</v>
@@ -14837,7 +14833,7 @@
         <v>21</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>75</v>
@@ -14846,7 +14842,7 @@
         <v>82</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AJ121" t="s" s="2">
         <v>95</v>
@@ -14854,10 +14850,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14880,16 +14876,16 @@
         <v>21</v>
       </c>
       <c r="K122" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="L122" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="L122" t="s" s="2">
+      <c r="M122" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="N122" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>622</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -14939,7 +14935,7 @@
         <v>21</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>75</v>
@@ -14948,7 +14944,7 @@
         <v>82</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>95</v>
@@ -14956,10 +14952,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14982,16 +14978,16 @@
         <v>21</v>
       </c>
       <c r="K123" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="L123" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="L123" t="s" s="2">
+      <c r="M123" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>628</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -15041,7 +15037,7 @@
         <v>21</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>75</v>
@@ -15050,7 +15046,7 @@
         <v>82</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="AJ123" t="s" s="2">
         <v>95</v>
@@ -15058,10 +15054,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15087,13 +15083,13 @@
         <v>422</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="M124" t="s" s="2">
+      <c r="N124" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>633</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -15143,7 +15139,7 @@
         <v>21</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>75</v>
@@ -15152,7 +15148,7 @@
         <v>76</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="AJ124" t="s" s="2">
         <v>95</v>
@@ -15160,10 +15156,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15260,10 +15256,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15362,10 +15358,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15466,10 +15462,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15492,16 +15488,16 @@
         <v>21</v>
       </c>
       <c r="K128" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="L128" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="L128" t="s" s="2">
+      <c r="M128" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="M128" t="s" s="2">
+      <c r="N128" t="s" s="2">
         <v>640</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>641</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -15530,11 +15526,11 @@
         <v>153</v>
       </c>
       <c r="Y128" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="Z128" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="Z128" t="s" s="2">
-        <v>592</v>
-      </c>
       <c r="AA128" t="s" s="2">
         <v>21</v>
       </c>
@@ -15551,7 +15547,7 @@
         <v>21</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>82</v>
@@ -15568,10 +15564,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -15597,20 +15593,20 @@
         <v>278</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="M129" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="M129" t="s" s="2">
+      <c r="N129" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>645</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q129" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="R129" t="s" s="2">
         <v>21</v>
@@ -15655,7 +15651,7 @@
         <v>21</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>75</v>
@@ -15672,10 +15668,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15701,16 +15697,16 @@
         <v>422</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="M130" t="s" s="2">
+      <c r="N130" t="s" s="2">
         <v>649</v>
       </c>
-      <c r="N130" t="s" s="2">
+      <c r="O130" t="s" s="2">
         <v>650</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>651</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>21</v>
@@ -15759,7 +15755,7 @@
         <v>21</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>75</v>
@@ -15768,7 +15764,7 @@
         <v>76</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AJ130" t="s" s="2">
         <v>95</v>
@@ -15776,10 +15772,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15876,10 +15872,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15978,10 +15974,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -16082,10 +16078,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16108,16 +16104,16 @@
         <v>21</v>
       </c>
       <c r="K134" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="L134" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="L134" t="s" s="2">
+      <c r="M134" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -16146,11 +16142,11 @@
         <v>153</v>
       </c>
       <c r="Y134" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="Z134" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="Z134" t="s" s="2">
-        <v>592</v>
-      </c>
       <c r="AA134" t="s" s="2">
         <v>21</v>
       </c>
@@ -16167,7 +16163,7 @@
         <v>21</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>82</v>
@@ -16184,10 +16180,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16213,16 +16209,16 @@
         <v>21</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>662</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="N135" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="N135" t="s" s="2">
+      <c r="O135" t="s" s="2">
         <v>664</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>665</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>21</v>
@@ -16271,7 +16267,7 @@
         <v>21</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>75</v>
@@ -16280,7 +16276,7 @@
         <v>76</v>
       </c>
       <c r="AI135" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="AJ135" t="s" s="2">
         <v>21</v>

--- a/output/StructureDefinition-ConsentModule.xlsx
+++ b/output/StructureDefinition-ConsentModule.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$133</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4383" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4315" uniqueCount="667">
   <si>
     <t>Property</t>
   </si>
@@ -1705,6 +1705,12 @@
     <t>Questionnaire.item.text.extension.extension</t>
   </si>
   <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
     <t>Questionnaire.item.text.extension:renderingMarkdown.url</t>
   </si>
   <si>
@@ -1720,10 +1726,15 @@
     <t>Questionnaire.item.text.extension.value[x]</t>
   </si>
   <si>
-    <t>Questionnaire.item.text.extension:renderingMarkdown.value[x]:valueMarkdown</t>
-  </si>
-  <si>
-    <t>valueMarkdown</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ext-1
+</t>
   </si>
   <si>
     <t>Questionnaire.item.text.extension:renderingXhtml</t>
@@ -1755,12 +1766,6 @@
   </si>
   <si>
     <t>Questionnaire.item.text.extension:renderingXhtml.value[x]</t>
-  </si>
-  <si>
-    <t>Questionnaire.item.text.extension:renderingXhtml.value[x]:valueString</t>
-  </si>
-  <si>
-    <t>valueString</t>
   </si>
   <si>
     <t>Questionnaire.item.text.value</t>
@@ -2426,10 +2431,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ135"/>
+  <dimension ref="A1:AJ133"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="66.02734375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="63.38671875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="43.50390625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="17.5" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
@@ -12428,7 +12433,7 @@
         <v>21</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="L98" t="s" s="2">
         <v>98</v>
@@ -12494,7 +12499,7 @@
         <v>82</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>21</v>
@@ -12509,7 +12514,7 @@
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -12531,14 +12536,12 @@
         <v>103</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>104</v>
+        <v>538</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>106</v>
-      </c>
+        <v>539</v>
+      </c>
+      <c r="N99" s="2"/>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>21</v>
@@ -12596,7 +12599,7 @@
         <v>76</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>111</v>
@@ -12604,10 +12607,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12647,7 +12650,7 @@
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>21</v>
@@ -12706,10 +12709,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12738,7 +12741,7 @@
         <v>455</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>456</v>
+        <v>545</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -12777,16 +12780,14 @@
         <v>21</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>546</v>
+      </c>
+      <c r="AC101" s="2"/>
       <c r="AD101" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>21</v>
+        <v>109</v>
       </c>
       <c r="AF101" t="s" s="2">
         <v>457</v>
@@ -12798,7 +12799,7 @@
         <v>82</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>94</v>
+        <v>547</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>95</v>
@@ -12806,20 +12807,20 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>542</v>
+        <v>528</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="D102" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>82</v>
@@ -12834,13 +12835,13 @@
         <v>21</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>305</v>
+        <v>550</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>455</v>
+        <v>551</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>456</v>
+        <v>552</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -12891,31 +12892,29 @@
         <v>21</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>457</v>
+        <v>110</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="C103" t="s" s="2">
-        <v>546</v>
-      </c>
+        <v>535</v>
+      </c>
+      <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
         <v>21</v>
       </c>
@@ -12936,13 +12935,13 @@
         <v>21</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>547</v>
+        <v>84</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>548</v>
+        <v>98</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>549</v>
+        <v>99</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -12993,27 +12992,27 @@
         <v>21</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13024,7 +13023,7 @@
         <v>75</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>21</v>
@@ -13036,13 +13035,13 @@
         <v>21</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>98</v>
+        <v>538</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>99</v>
+        <v>539</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -13081,50 +13080,50 @@
         <v>21</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>21</v>
+        <v>109</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>21</v>
@@ -13136,16 +13135,16 @@
         <v>21</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>104</v>
+        <v>448</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>105</v>
+        <v>449</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>106</v>
+        <v>450</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -13153,7 +13152,7 @@
       </c>
       <c r="Q105" s="2"/>
       <c r="R105" t="s" s="2">
-        <v>21</v>
+        <v>556</v>
       </c>
       <c r="S105" t="s" s="2">
         <v>21</v>
@@ -13183,39 +13182,39 @@
         <v>21</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>110</v>
+        <v>451</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13238,24 +13237,22 @@
         <v>21</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>450</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
-        <v>553</v>
+        <v>21</v>
       </c>
       <c r="S106" t="s" s="2">
         <v>21</v>
@@ -13285,39 +13282,37 @@
         <v>21</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>546</v>
+      </c>
+      <c r="AC106" s="2"/>
       <c r="AD106" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>21</v>
+        <v>109</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>21</v>
+        <v>547</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>21</v>
+        <v>95</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>542</v>
+        <v>558</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13325,7 +13320,7 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G107" t="s" s="2">
         <v>82</v>
@@ -13343,10 +13338,10 @@
         <v>97</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>455</v>
+        <v>559</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>456</v>
+        <v>559</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -13370,7 +13365,7 @@
         <v>21</v>
       </c>
       <c r="W107" t="s" s="2">
-        <v>21</v>
+        <v>560</v>
       </c>
       <c r="X107" t="s" s="2">
         <v>21</v>
@@ -13397,7 +13392,7 @@
         <v>21</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>457</v>
+        <v>561</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>75</v>
@@ -13406,22 +13401,20 @@
         <v>82</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>95</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="108" hidden="true">
+    <row r="108">
       <c r="A108" t="s" s="2">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="C108" t="s" s="2">
-        <v>556</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
         <v>21</v>
       </c>
@@ -13433,7 +13426,7 @@
         <v>82</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>21</v>
@@ -13442,16 +13435,20 @@
         <v>21</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>455</v>
+        <v>563</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
+        <v>564</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>566</v>
+      </c>
       <c r="P108" t="s" s="2">
         <v>21</v>
       </c>
@@ -13475,13 +13472,13 @@
         <v>21</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>21</v>
+        <v>211</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>21</v>
+        <v>567</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>21</v>
+        <v>568</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>21</v>
@@ -13499,10 +13496,10 @@
         <v>21</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>457</v>
+        <v>562</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>82</v>
@@ -13516,10 +13513,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13530,28 +13527,32 @@
         <v>75</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J109" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>97</v>
+        <v>422</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N109" s="2"/>
-      <c r="O109" s="2"/>
+        <v>571</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>573</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>21</v>
       </c>
@@ -13572,7 +13573,7 @@
         <v>21</v>
       </c>
       <c r="W109" t="s" s="2">
-        <v>559</v>
+        <v>21</v>
       </c>
       <c r="X109" t="s" s="2">
         <v>21</v>
@@ -13599,27 +13600,27 @@
         <v>21</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>21</v>
+        <v>574</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>561</v>
+        <v>575</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>561</v>
+        <v>575</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13627,13 +13628,13 @@
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>21</v>
@@ -13642,20 +13643,16 @@
         <v>21</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>163</v>
+        <v>97</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>562</v>
+        <v>98</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>565</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N110" s="2"/>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>21</v>
       </c>
@@ -13679,13 +13676,13 @@
         <v>21</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>211</v>
+        <v>21</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>566</v>
+        <v>21</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>567</v>
+        <v>21</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>21</v>
@@ -13703,31 +13700,31 @@
         <v>21</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>561</v>
+        <v>100</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>95</v>
+        <v>21</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -13740,26 +13737,24 @@
         <v>21</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J111" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>422</v>
+        <v>103</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>569</v>
+        <v>104</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>570</v>
+        <v>105</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>572</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>21</v>
       </c>
@@ -13795,19 +13790,19 @@
         <v>21</v>
       </c>
       <c r="AB111" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="AC111" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="AD111" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>21</v>
+        <v>109</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>568</v>
+        <v>110</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>75</v>
@@ -13819,47 +13814,51 @@
         <v>94</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>573</v>
+        <v>111</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>21</v>
+        <v>496</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I112" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>98</v>
+        <v>497</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N112" s="2"/>
-      <c r="O112" s="2"/>
+        <v>498</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>191</v>
+      </c>
       <c r="P112" t="s" s="2">
         <v>21</v>
       </c>
@@ -13907,38 +13906,38 @@
         <v>21</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>100</v>
+        <v>499</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>21</v>
@@ -13950,16 +13949,16 @@
         <v>21</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>104</v>
+        <v>579</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>105</v>
+        <v>580</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>106</v>
+        <v>581</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -13997,75 +13996,73 @@
         <v>21</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>110</v>
+        <v>578</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>496</v>
+        <v>21</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I114" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>103</v>
+        <v>163</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>497</v>
+        <v>583</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>498</v>
+        <v>584</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>191</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>21</v>
       </c>
@@ -14089,13 +14086,13 @@
         <v>21</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>21</v>
+        <v>211</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>21</v>
+        <v>585</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>21</v>
+        <v>586</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>21</v>
@@ -14113,27 +14110,27 @@
         <v>21</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>499</v>
+        <v>582</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14156,17 +14153,15 @@
         <v>21</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>97</v>
+        <v>588</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>580</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>21</v>
@@ -14191,13 +14186,13 @@
         <v>21</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>21</v>
+        <v>591</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>21</v>
+        <v>592</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>21</v>
@@ -14215,7 +14210,7 @@
         <v>21</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>82</v>
@@ -14224,7 +14219,7 @@
         <v>82</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>94</v>
+        <v>593</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>95</v>
@@ -14232,10 +14227,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>581</v>
+        <v>594</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>581</v>
+        <v>594</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14243,7 +14238,7 @@
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G116" t="s" s="2">
         <v>82</v>
@@ -14261,13 +14256,13 @@
         <v>163</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>582</v>
+        <v>595</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>583</v>
+        <v>596</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>340</v>
+        <v>597</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -14296,10 +14291,10 @@
         <v>211</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>585</v>
+        <v>598</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>21</v>
@@ -14317,16 +14312,16 @@
         <v>21</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>581</v>
+        <v>594</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>94</v>
+        <v>599</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>95</v>
@@ -14334,10 +14329,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>586</v>
+        <v>600</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>586</v>
+        <v>600</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14345,7 +14340,7 @@
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G117" t="s" s="2">
         <v>82</v>
@@ -14360,20 +14355,24 @@
         <v>21</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>587</v>
+        <v>278</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>588</v>
+        <v>601</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="N117" s="2"/>
+        <v>602</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>603</v>
+      </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q117" s="2"/>
+      <c r="Q117" t="s" s="2">
+        <v>604</v>
+      </c>
       <c r="R117" t="s" s="2">
         <v>21</v>
       </c>
@@ -14393,13 +14392,13 @@
         <v>21</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>590</v>
+        <v>21</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>591</v>
+        <v>21</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>21</v>
@@ -14417,16 +14416,16 @@
         <v>21</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>586</v>
+        <v>600</v>
       </c>
       <c r="AG117" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH117" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>592</v>
+        <v>605</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>95</v>
@@ -14434,10 +14433,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>593</v>
+        <v>606</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>593</v>
+        <v>606</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14460,22 +14459,26 @@
         <v>21</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>163</v>
+        <v>278</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>594</v>
+        <v>607</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>595</v>
+        <v>608</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="O118" s="2"/>
+        <v>609</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>610</v>
+      </c>
       <c r="P118" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q118" s="2"/>
+      <c r="Q118" t="s" s="2">
+        <v>611</v>
+      </c>
       <c r="R118" t="s" s="2">
         <v>21</v>
       </c>
@@ -14495,13 +14498,13 @@
         <v>21</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>211</v>
+        <v>21</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>595</v>
+        <v>21</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>597</v>
+        <v>21</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>21</v>
@@ -14519,7 +14522,7 @@
         <v>21</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>593</v>
+        <v>606</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>75</v>
@@ -14528,7 +14531,7 @@
         <v>82</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>95</v>
@@ -14536,10 +14539,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>599</v>
+        <v>612</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>599</v>
+        <v>612</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14565,21 +14568,21 @@
         <v>278</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>600</v>
+        <v>613</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>601</v>
+        <v>614</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="O119" s="2"/>
+        <v>615</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>616</v>
+      </c>
       <c r="P119" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q119" t="s" s="2">
-        <v>603</v>
-      </c>
+      <c r="Q119" s="2"/>
       <c r="R119" t="s" s="2">
         <v>21</v>
       </c>
@@ -14623,7 +14626,7 @@
         <v>21</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>599</v>
+        <v>612</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>75</v>
@@ -14632,7 +14635,7 @@
         <v>82</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>604</v>
+        <v>617</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>95</v>
@@ -14640,10 +14643,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>605</v>
+        <v>618</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>605</v>
+        <v>618</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14666,26 +14669,22 @@
         <v>21</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>278</v>
+        <v>619</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>606</v>
+        <v>620</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>607</v>
+        <v>621</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>609</v>
-      </c>
+        <v>622</v>
+      </c>
+      <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q120" t="s" s="2">
-        <v>610</v>
-      </c>
+      <c r="Q120" s="2"/>
       <c r="R120" t="s" s="2">
         <v>21</v>
       </c>
@@ -14729,7 +14728,7 @@
         <v>21</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>605</v>
+        <v>618</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>75</v>
@@ -14738,7 +14737,7 @@
         <v>82</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>604</v>
+        <v>623</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>95</v>
@@ -14746,10 +14745,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>611</v>
+        <v>624</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>611</v>
+        <v>624</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14772,20 +14771,18 @@
         <v>21</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>278</v>
+        <v>625</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>612</v>
+        <v>626</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>613</v>
+        <v>627</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>615</v>
-      </c>
+        <v>628</v>
+      </c>
+      <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>21</v>
       </c>
@@ -14833,7 +14830,7 @@
         <v>21</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>611</v>
+        <v>624</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>75</v>
@@ -14842,7 +14839,7 @@
         <v>82</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>616</v>
+        <v>629</v>
       </c>
       <c r="AJ121" t="s" s="2">
         <v>95</v>
@@ -14850,10 +14847,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>617</v>
+        <v>630</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>617</v>
+        <v>630</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14864,7 +14861,7 @@
         <v>75</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>21</v>
@@ -14876,16 +14873,16 @@
         <v>21</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>618</v>
+        <v>422</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>620</v>
+        <v>632</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>621</v>
+        <v>633</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -14935,16 +14932,16 @@
         <v>21</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>617</v>
+        <v>630</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>95</v>
@@ -14952,10 +14949,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14978,17 +14975,15 @@
         <v>21</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>624</v>
+        <v>97</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>625</v>
+        <v>98</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>627</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N123" s="2"/>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>21</v>
@@ -15037,7 +15032,7 @@
         <v>21</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>623</v>
+        <v>100</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>75</v>
@@ -15046,22 +15041,22 @@
         <v>82</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>628</v>
+        <v>21</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>95</v>
+        <v>21</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
@@ -15080,16 +15075,16 @@
         <v>21</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>422</v>
+        <v>103</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>630</v>
+        <v>104</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>631</v>
+        <v>105</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>632</v>
+        <v>106</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -15127,19 +15122,19 @@
         <v>21</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="AC124" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="AD124" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE124" t="s" s="2">
-        <v>21</v>
+        <v>109</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>629</v>
+        <v>110</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>75</v>
@@ -15148,50 +15143,54 @@
         <v>76</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>628</v>
+        <v>94</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>21</v>
+        <v>496</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I125" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>98</v>
+        <v>497</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N125" s="2"/>
-      <c r="O125" s="2"/>
+        <v>498</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>191</v>
+      </c>
       <c r="P125" t="s" s="2">
         <v>21</v>
       </c>
@@ -15239,38 +15238,38 @@
         <v>21</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>100</v>
+        <v>499</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>21</v>
@@ -15282,16 +15281,16 @@
         <v>21</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>103</v>
+        <v>638</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>104</v>
+        <v>639</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>105</v>
+        <v>640</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>106</v>
+        <v>641</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -15317,91 +15316,91 @@
         <v>21</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>21</v>
+        <v>591</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>21</v>
+        <v>592</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB126" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="AC126" t="s" s="2">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="AD126" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE126" t="s" s="2">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>110</v>
+        <v>637</v>
       </c>
       <c r="AG126" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>496</v>
+        <v>21</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I127" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>103</v>
+        <v>278</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>497</v>
+        <v>643</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>498</v>
+        <v>644</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>191</v>
-      </c>
+        <v>645</v>
+      </c>
+      <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q127" s="2"/>
+      <c r="Q127" t="s" s="2">
+        <v>646</v>
+      </c>
       <c r="R127" t="s" s="2">
         <v>21</v>
       </c>
@@ -15445,27 +15444,27 @@
         <v>21</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>499</v>
+        <v>642</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>636</v>
+        <v>647</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>636</v>
+        <v>647</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15473,10 +15472,10 @@
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>21</v>
@@ -15488,18 +15487,20 @@
         <v>21</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>637</v>
+        <v>422</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>638</v>
+        <v>648</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>639</v>
+        <v>649</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="O128" s="2"/>
+        <v>650</v>
+      </c>
+      <c r="O128" t="s" s="2">
+        <v>651</v>
+      </c>
       <c r="P128" t="s" s="2">
         <v>21</v>
       </c>
@@ -15523,13 +15524,13 @@
         <v>21</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>590</v>
+        <v>21</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>591</v>
+        <v>21</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>21</v>
@@ -15547,16 +15548,16 @@
         <v>21</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>636</v>
+        <v>647</v>
       </c>
       <c r="AG128" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>94</v>
+        <v>652</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>95</v>
@@ -15564,10 +15565,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>641</v>
+        <v>653</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>641</v>
+        <v>653</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -15590,24 +15591,20 @@
         <v>21</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>278</v>
+        <v>97</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>642</v>
+        <v>98</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>644</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N129" s="2"/>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q129" t="s" s="2">
-        <v>645</v>
-      </c>
+      <c r="Q129" s="2"/>
       <c r="R129" t="s" s="2">
         <v>21</v>
       </c>
@@ -15651,7 +15648,7 @@
         <v>21</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>641</v>
+        <v>100</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>75</v>
@@ -15660,22 +15657,22 @@
         <v>82</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>95</v>
+        <v>21</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -15694,20 +15691,18 @@
         <v>21</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>422</v>
+        <v>103</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>647</v>
+        <v>104</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>648</v>
+        <v>105</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>650</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>21</v>
       </c>
@@ -15743,19 +15738,19 @@
         <v>21</v>
       </c>
       <c r="AB130" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="AC130" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="AD130" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE130" t="s" s="2">
-        <v>21</v>
+        <v>109</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>646</v>
+        <v>110</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>75</v>
@@ -15764,50 +15759,54 @@
         <v>76</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>651</v>
+        <v>94</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>21</v>
+        <v>496</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I131" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>98</v>
+        <v>497</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N131" s="2"/>
-      <c r="O131" s="2"/>
+        <v>498</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="O131" t="s" s="2">
+        <v>191</v>
+      </c>
       <c r="P131" t="s" s="2">
         <v>21</v>
       </c>
@@ -15855,38 +15854,38 @@
         <v>21</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>100</v>
+        <v>499</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>21</v>
@@ -15898,16 +15897,16 @@
         <v>21</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>103</v>
+        <v>657</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>104</v>
+        <v>658</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>105</v>
+        <v>659</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>106</v>
+        <v>660</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -15933,86 +15932,86 @@
         <v>21</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>21</v>
+        <v>591</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>21</v>
+        <v>592</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB132" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="AC132" t="s" s="2">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="AD132" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE132" t="s" s="2">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>110</v>
+        <v>656</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>496</v>
+        <v>21</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I133" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>497</v>
+        <v>662</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>498</v>
+        <v>663</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>106</v>
+        <v>664</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>191</v>
+        <v>665</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>21</v>
@@ -16061,7 +16060,7 @@
         <v>21</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>499</v>
+        <v>661</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>75</v>
@@ -16070,220 +16069,14 @@
         <v>76</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>94</v>
+        <v>666</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="134" hidden="true">
-      <c r="A134" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="C134" s="2"/>
-      <c r="D134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E134" s="2"/>
-      <c r="F134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K134" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="L134" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="O134" s="2"/>
-      <c r="P134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q134" s="2"/>
-      <c r="R134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X134" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y134" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="Z134" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="AA134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF134" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="AG134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI134" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AJ134" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="135" hidden="true">
-      <c r="A135" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="B135" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="C135" s="2"/>
-      <c r="D135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E135" s="2"/>
-      <c r="F135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="L135" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="P135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q135" s="2"/>
-      <c r="R135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF135" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="AG135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH135" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI135" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="AJ135" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ135">
+  <autoFilter ref="A1:AJ133">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16293,7 +16086,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI134">
+  <conditionalFormatting sqref="A2:AI132">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
